--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105715</v>
+        <v>105717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129237096</v>
       </c>
       <c r="B4" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97538</v>
+        <v>97540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105717</v>
+        <v>105724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129236984</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105724</v>
+        <v>105726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129237096</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105726</v>
+        <v>105752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105752</v>
+        <v>105754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105754</v>
+        <v>105755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105755</v>
+        <v>105759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129237096</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129236984</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129237058</v>
       </c>
       <c r="B3" t="n">
-        <v>105807</v>
+        <v>105819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129237096</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129237081</v>
       </c>
       <c r="B5" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129236984</v>
+        <v>129237059</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>101298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älvsbyn, Älvsbyn, Nb</t>
+          <t>Älvsbyn, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773777</v>
+        <v>773664</v>
       </c>
       <c r="R2" t="n">
-        <v>7298310</v>
+        <v>7298263</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129237058</v>
+        <v>129237096</v>
       </c>
       <c r="B3" t="n">
-        <v>105819</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,7 +816,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>773680</v>
+        <v>773603</v>
       </c>
       <c r="R3" t="n">
-        <v>7298280</v>
+        <v>7298260</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129237096</v>
+        <v>129237269</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>58388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,21 +920,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älvsbyn, Nb</t>
+          <t>Älvsbyn, Älvsbyn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>773603</v>
       </c>
       <c r="R4" t="n">
-        <v>7298260</v>
+        <v>7298452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129237081</v>
+        <v>129236984</v>
       </c>
       <c r="B5" t="n">
-        <v>97639</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,24 +1031,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älvsbyn, Nb</t>
+          <t>Älvsbyn, Älvsbyn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>773679</v>
+        <v>773777</v>
       </c>
       <c r="R5" t="n">
-        <v>7298277</v>
+        <v>7298310</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,6 +1106,647 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129237002</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Älvsbyn, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>773494</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7298205</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129237055</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>773705</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7298288</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129237054</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>773742</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7298296</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129237056</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>773702</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7298284</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129237058</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>773680</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7298280</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129237057</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>773679</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7298277</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11477-2022 artfynd.xlsx
+++ b/artfynd/A 11477-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237096</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129236984</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237002</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237055</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237054</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237056</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,8 +1797,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237057</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>